--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_136_R14.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_136_R14.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9073</v>
+        <v>4.6658</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2455</v>
+        <v>5.0712</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3382</v>
+        <v>-0.4054</v>
       </c>
       <c r="G2" t="n">
         <v>2.648</v>
@@ -610,13 +610,13 @@
         <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7407</v>
+        <v>0.0178</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9392</v>
+        <v>-0.1136</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1986</v>
+        <v>0.1314</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. DESSERT</t>
+          <t>R. BEAUBOIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9974</v>
+        <v>2.0198</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9708</v>
+        <v>1.4854</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0266</v>
+        <v>0.5344</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2799</v>
+        <v>2.2645</v>
       </c>
       <c r="H3" t="n">
-        <v>0.755</v>
+        <v>0.0228</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4751</v>
+        <v>2.2417</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7765</v>
+        <v>3.73</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7765</v>
+        <v>0.5917</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.1383</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4966</v>
+        <v>-1.4655</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0216</v>
+        <v>-0.5688</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4751</v>
+        <v>-0.8966</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4639</v>
+        <v>0.4639</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>-1.6237</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6959</v>
+        <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1092</v>
+        <v>-0.7086</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2819</v>
+        <v>-0.621</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1726</v>
+        <v>-0.0876</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. BEAUBOIS</t>
+          <t>B. DESSERT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8011</v>
+        <v>1.3905</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3674</v>
+        <v>1.2631</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4336</v>
+        <v>0.1274</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2645</v>
+        <v>0.2799</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0228</v>
+        <v>0.755</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2417</v>
+        <v>-0.4751</v>
       </c>
       <c r="J4" t="n">
-        <v>3.73</v>
+        <v>0.7765</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5917</v>
+        <v>0.7765</v>
       </c>
       <c r="L4" t="n">
-        <v>3.1383</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4655</v>
+        <v>-0.4966</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5688</v>
+        <v>-0.0216</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8966</v>
+        <v>-0.4751</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4639</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.6237</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9274</v>
+        <v>0.5023</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7389</v>
+        <v>0.5742</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1885</v>
+        <v>-0.0718</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3526</v>
+        <v>-0.0184</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6538</v>
+        <v>0.182</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3012</v>
+        <v>-0.2004</v>
       </c>
       <c r="G5" t="n">
         <v>0.6459</v>
@@ -844,13 +844,13 @@
         <v>0.232</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.1759</v>
       </c>
       <c r="T5" t="n">
-        <v>0.637</v>
+        <v>0.1652</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0901</v>
+        <v>0.0108</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0722</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5233</v>
+        <v>-1.4389</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6453</v>
+        <v>-0.5273</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.878</v>
+        <v>-0.9116</v>
       </c>
       <c r="G8" t="n">
         <v>-3.9059</v>
@@ -1078,13 +1078,13 @@
         <v>2.3195</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6146</v>
+        <v>0.6989</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2952</v>
+        <v>0.4132</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3194</v>
+        <v>0.2858</v>
       </c>
       <c r="V8" t="n">
         <v>1.0722</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3304</v>
+        <v>-2.078</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4964</v>
+        <v>-2.3784</v>
       </c>
       <c r="F9" t="n">
-        <v>0.166</v>
+        <v>0.3004</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9719</v>
@@ -1156,13 +1156,13 @@
         <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5904</v>
+        <v>-0.338</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5228</v>
+        <v>-0.4048</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0677</v>
+        <v>0.0668</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5361</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4933</v>
+        <v>-3.1674</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.905</v>
+        <v>-2.6127</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.5546</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4856</v>
@@ -1234,13 +1234,13 @@
         <v>1.8556</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2217</v>
+        <v>0.5476</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7749</v>
+        <v>0.0672</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4468</v>
+        <v>0.4804</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9794</v>
+        <v>-4.2374</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2044</v>
+        <v>-3.2608</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.775</v>
+        <v>-0.9766</v>
       </c>
       <c r="G11" t="n">
         <v>-3.2263</v>
@@ -1312,13 +1312,13 @@
         <v>2.5515</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6808999999999999</v>
+        <v>0.0611</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1633</v>
+        <v>-0.2197</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4824</v>
+        <v>0.2807</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.3852</v>
+        <v>-6.7891</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.9246</v>
+        <v>-6.1605</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4606</v>
+        <v>-0.6286</v>
       </c>
       <c r="G12" t="n">
         <v>-6.9797</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2208</v>
+        <v>0.8169</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7749</v>
+        <v>0.539</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4459</v>
+        <v>0.2779</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3943</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.1725</v>
+        <v>-11.1724</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.667199999999999</v>
+        <v>-7.667000000000001</v>
       </c>
       <c r="F13" t="n">
         <v>-3.5053</v>
@@ -1438,13 +1438,13 @@
         <v>-9.4361</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.8402</v>
+        <v>-1.840200000000001</v>
       </c>
       <c r="J13" t="n">
         <v>4.432100000000002</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.961499999999999</v>
+        <v>-2.9615</v>
       </c>
       <c r="L13" t="n">
         <v>7.393600000000003</v>
@@ -1468,13 +1468,13 @@
         <v>16.2368</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3178</v>
+        <v>1.3179</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1009000000000001</v>
+        <v>0.1009</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2169</v>
+        <v>1.2171</v>
       </c>
       <c r="V13" t="n">
         <v>-1.214</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8866</v>
+        <v>4.7448</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4323</v>
+        <v>3.4431</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4544</v>
+        <v>1.3017</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9222</v>
+        <v>5.2016</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5739</v>
+        <v>0.969</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3483</v>
+        <v>4.2326</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8947</v>
+        <v>5.8093</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8605</v>
+        <v>0.9411</v>
       </c>
       <c r="L14" t="n">
-        <v>2.0342</v>
+        <v>4.8682</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9725</v>
+        <v>-0.6077</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2866</v>
+        <v>0.0279</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6859</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>1.6237</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3407</v>
+        <v>-0.1346</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5375</v>
+        <v>-0.1885</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1968</v>
+        <v>0.0538</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0612</v>
+        <v>3.9823</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7354</v>
+        <v>3.3707</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3258</v>
+        <v>0.6116</v>
       </c>
       <c r="G15" t="n">
-        <v>5.2016</v>
+        <v>1.9222</v>
       </c>
       <c r="H15" t="n">
-        <v>0.969</v>
+        <v>0.5739</v>
       </c>
       <c r="I15" t="n">
-        <v>4.2326</v>
+        <v>1.3483</v>
       </c>
       <c r="J15" t="n">
-        <v>5.8093</v>
+        <v>2.8947</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9411</v>
+        <v>0.8605</v>
       </c>
       <c r="L15" t="n">
-        <v>4.8682</v>
+        <v>2.0342</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6077</v>
+        <v>-0.9725</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0279</v>
+        <v>-0.2866</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.6859</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.8183</v>
+        <v>0.4364</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8962</v>
+        <v>0.476</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9221</v>
+        <v>-0.0395</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. HEZONJA</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7953</v>
+        <v>3.2529</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8563</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9389999999999999</v>
+        <v>2.7524</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4169</v>
+        <v>2.1402</v>
       </c>
       <c r="H16" t="n">
-        <v>0.235</v>
+        <v>2.3074</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1819</v>
+        <v>-0.1672</v>
       </c>
       <c r="J16" t="n">
-        <v>4.2856</v>
+        <v>2.0541</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5216</v>
+        <v>1.4284</v>
       </c>
       <c r="L16" t="n">
-        <v>3.764</v>
+        <v>0.6257</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8687</v>
+        <v>0.0861</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2866</v>
+        <v>0.8789</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5821</v>
+        <v>-0.7929</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1577</v>
+        <v>0.2003</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1098</v>
+        <v>-0.4481</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0479</v>
+        <v>0.6484</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>M. HEZONJA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7811</v>
+        <v>3.2449</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5004999999999999</v>
+        <v>2.0922</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2806</v>
+        <v>1.1527</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1402</v>
+        <v>3.4169</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3074</v>
+        <v>0.235</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1672</v>
+        <v>3.1819</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0541</v>
+        <v>4.2856</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4284</v>
+        <v>0.5216</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6257</v>
+        <v>3.764</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0861</v>
+        <v>-0.8687</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8789</v>
+        <v>-0.2866</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7929</v>
+        <v>-0.5821</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2715</v>
+        <v>0.2919</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4481</v>
+        <v>0.1261</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1766</v>
+        <v>0.1658</v>
       </c>
       <c r="V17" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5324</v>
+        <v>1.9757</v>
       </c>
       <c r="E18" t="n">
-        <v>0.227</v>
+        <v>0.345</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3054</v>
+        <v>1.6307</v>
       </c>
       <c r="G18" t="n">
         <v>1.1318</v>
@@ -1858,13 +1858,13 @@
         <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5091</v>
+        <v>-0.0659</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5228</v>
+        <v>-0.4048</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0136</v>
+        <v>0.3389</v>
       </c>
       <c r="V18" t="n">
         <v>0.6778999999999999</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.254</v>
+        <v>1.0651</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4334</v>
+        <v>-1.1975</v>
       </c>
       <c r="F19" t="n">
-        <v>2.6874</v>
+        <v>2.2626</v>
       </c>
       <c r="G19" t="n">
         <v>1.2824</v>
@@ -1936,13 +1936,13 @@
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0438</v>
+        <v>0.8549</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4481</v>
+        <v>-0.2122</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4919</v>
+        <v>1.0671</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0722</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9032</v>
+        <v>0.9203</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0588</v>
+        <v>1.1768</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1556</v>
+        <v>-0.2564</v>
       </c>
       <c r="G20" t="n">
         <v>0.6717</v>
@@ -2014,13 +2014,13 @@
         <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0004</v>
+        <v>0.0167</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1494</v>
+        <v>-0.0314</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1489</v>
+        <v>0.0481</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4684</v>
+        <v>0.4976</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6452</v>
+        <v>-0.5273</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1136</v>
+        <v>1.0249</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1248</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2891</v>
+        <v>0.3183</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5228</v>
+        <v>-0.4048</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8118</v>
+        <v>0.7231</v>
       </c>
       <c r="V21" t="n">
         <v>1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1173</v>
+        <v>0.241</v>
       </c>
       <c r="E22" t="n">
         <v>0.9219000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8046</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>0.6812</v>
@@ -2170,13 +2170,13 @@
         <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1876</v>
+        <v>-0.0639</v>
       </c>
       <c r="T22" t="n">
         <v>-0.224</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0365</v>
+        <v>0.1601</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.961</v>
+        <v>-0.1979</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5842000000000001</v>
+        <v>-1.9209</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5452</v>
+        <v>1.723</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.7528</v>
+        <v>1.9048</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.468</v>
+        <v>2.7814</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.2848</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3911</v>
+        <v>1.9761</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6855</v>
+        <v>1.9024</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2944</v>
+        <v>0.0736</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3617</v>
+        <v>-0.0712</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2175</v>
+        <v>0.8789</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.5792</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>1.3917</v>
+        <v>-3.0154</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4722</v>
+        <v>-0.0178</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9752</v>
+        <v>-0.3301</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.503</v>
+        <v>0.3123</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0722</v>
+        <v>0.9304</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2581</v>
+        <v>-1.4107</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0388</v>
+        <v>-0.1235</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7806999999999999</v>
+        <v>-1.2871</v>
       </c>
       <c r="G24" t="n">
-        <v>1.9048</v>
+        <v>-1.7528</v>
       </c>
       <c r="H24" t="n">
-        <v>2.7814</v>
+        <v>-0.468</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8764999999999999</v>
+        <v>-1.2848</v>
       </c>
       <c r="J24" t="n">
-        <v>1.9761</v>
+        <v>-0.3911</v>
       </c>
       <c r="K24" t="n">
-        <v>1.9024</v>
+        <v>-0.6855</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0736</v>
+        <v>0.2944</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0712</v>
+        <v>-1.3617</v>
       </c>
       <c r="N24" t="n">
-        <v>0.8789</v>
+        <v>0.2175</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-1.5792</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.0154</v>
+        <v>1.3917</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.639</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.078</v>
+        <v>0.0226</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4481</v>
+        <v>0.2675</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.63</v>
+        <v>-0.2449</v>
       </c>
       <c r="V24" t="n">
-        <v>0.9304</v>
+        <v>-1.0722</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.408</v>
+        <v>-3.9983</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.6935</v>
+        <v>-4.5755</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2855</v>
+        <v>0.5772</v>
       </c>
       <c r="G25" t="n">
         <v>-4.1989</v>
@@ -2404,13 +2404,13 @@
         <v>1.3917</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4411</v>
+        <v>-0.0314</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0395</v>
+        <v>0.1575</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4806</v>
+        <v>-0.1889</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>11.1724</v>
+        <v>14.3177</v>
       </c>
       <c r="E26" t="n">
-        <v>3.5055</v>
+        <v>3.505500000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>7.667000000000001</v>
+        <v>10.8124</v>
       </c>
       <c r="G26" t="n">
         <v>11.2763</v>
@@ -2467,13 +2467,13 @@
         <v>-4.4321</v>
       </c>
       <c r="N26" t="n">
-        <v>2.9614</v>
+        <v>2.961399999999999</v>
       </c>
       <c r="O26" t="n">
         <v>-7.393599999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0001999999999997837</v>
+        <v>0.0002000000000000057</v>
       </c>
       <c r="Q26" t="n">
         <v>-16.2367</v>
@@ -2482,13 +2482,13 @@
         <v>16.2368</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.3179</v>
+        <v>1.8275</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.2171</v>
+        <v>-1.2168</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1011</v>
+        <v>3.0443</v>
       </c>
       <c r="V26" t="n">
         <v>1.214</v>
